--- a/outputs/bank_peer_report.xlsx
+++ b/outputs/bank_peer_report.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Medians (Latest)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Banks (Latest)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Trends" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Peer Medians (Latest)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All Banks (Latest)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Watchlist" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Peer Trends" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Definitions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Peer Medians (Latest)'!$A$1:$I$4</definedName>
@@ -29,16 +29,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -63,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -71,24 +68,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -67103,12 +67094,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>BayCoast Bank</t>
+          <t>Industrial and Commercial Bank of China USA, National Association</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -67120,16 +67111,16 @@
         <v>2.86</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>0.5090433189373119</v>
+        <v>0.6656889350773629</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1.454210849955982</v>
+        <v>4.20456752393268</v>
       </c>
       <c r="G114" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>8.291879818761434</v>
+        <v>17.25538300510983</v>
       </c>
       <c r="I114" s="2" t="n">
         <v>1</v>
@@ -67143,12 +67134,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Commercial Bank of China USA, National Association</t>
+          <t>BayCoast Bank</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -67160,16 +67151,16 @@
         <v>2.86</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>0.6656889350773629</v>
+        <v>0.5090433189373119</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>4.20456752393268</v>
+        <v>1.454210849955982</v>
       </c>
       <c r="G115" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>17.25538300510983</v>
+        <v>8.291879818761434</v>
       </c>
       <c r="I115" s="2" t="n">
         <v>1</v>
@@ -67663,12 +67654,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Fidelity Bank &amp; Trust</t>
+          <t>Dedham Institution for Savings</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -67680,16 +67671,16 @@
         <v>2.6</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>1.299257276220965</v>
+        <v>0.8805319205415725</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1.262121833628537</v>
+        <v>1.151368008217387</v>
       </c>
       <c r="G128" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>8.977787431003502</v>
+        <v>11.39483162870477</v>
       </c>
       <c r="I128" s="2" t="n">
         <v>1</v>
@@ -67703,12 +67694,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>KS StateBank</t>
+          <t>Fidelity Bank &amp; Trust</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -67720,16 +67711,16 @@
         <v>2.6</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>1.949015717547198</v>
+        <v>1.299257276220965</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>2.493799528159216</v>
+        <v>1.262121833628537</v>
       </c>
       <c r="G129" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H129" s="4" t="n">
-        <v>12.96524297547413</v>
+        <v>8.977787431003502</v>
       </c>
       <c r="I129" s="2" t="n">
         <v>1</v>
@@ -67743,12 +67734,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Dedham Institution for Savings</t>
+          <t>KS StateBank</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -67760,16 +67751,16 @@
         <v>2.6</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>0.8805319205415725</v>
+        <v>1.949015717547198</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1.151368008217387</v>
+        <v>2.493799528159216</v>
       </c>
       <c r="G130" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>11.39483162870477</v>
+        <v>12.96524297547413</v>
       </c>
       <c r="I130" s="2" t="n">
         <v>1</v>
@@ -67783,7 +67774,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Wells Fargo Bank South Central, National Association</t>
+          <t>State Bank of Texas</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -67800,16 +67791,16 @@
         <v>2.59</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>1.621537596044236</v>
+        <v>4.240736806108307</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1.238147618009484</v>
+        <v>2.15529406371281</v>
       </c>
       <c r="G131" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H131" s="4" t="n">
-        <v>29.69171119921634</v>
+        <v>15.70547302422191</v>
       </c>
       <c r="I131" s="2" t="n">
         <v>1</v>
@@ -67823,7 +67814,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>State Bank of Texas</t>
+          <t>Wells Fargo Bank South Central, National Association</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -67840,16 +67831,16 @@
         <v>2.59</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>4.240736806108307</v>
+        <v>1.621537596044236</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>2.15529406371281</v>
+        <v>1.238147618009484</v>
       </c>
       <c r="G132" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>15.70547302422191</v>
+        <v>29.69171119921634</v>
       </c>
       <c r="I132" s="2" t="n">
         <v>1</v>
@@ -67983,12 +67974,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Somerset Trust Company</t>
+          <t>Newtek Bank, National Association</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -68000,16 +67991,16 @@
         <v>2.47</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>1.157529144178948</v>
+        <v>4.402542597877482</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1.494812595623905</v>
+        <v>7.185663489314225</v>
       </c>
       <c r="G136" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>9.100596879444391</v>
+        <v>8.610542311625865</v>
       </c>
       <c r="I136" s="2" t="n">
         <v>1</v>
@@ -68023,12 +68014,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Newtek Bank, National Association</t>
+          <t>Somerset Trust Company</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -68040,16 +68031,16 @@
         <v>2.47</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>4.402542597877482</v>
+        <v>1.157529144178948</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>7.185663489314225</v>
+        <v>1.494812595623905</v>
       </c>
       <c r="G137" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>8.610542311625865</v>
+        <v>9.100596879444391</v>
       </c>
       <c r="I137" s="2" t="n">
         <v>1</v>
@@ -68263,12 +68254,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>The Bank of Commerce</t>
+          <t>Farmers and Merchants Trust Company of Chambersburg</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -68280,16 +68271,16 @@
         <v>2.34</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>2.129422997033723</v>
+        <v>1.26508929370285</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1.347775536702867</v>
+        <v>1.098972614626358</v>
       </c>
       <c r="G143" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>15.69355733030755</v>
+        <v>8.829927314414981</v>
       </c>
       <c r="I143" s="2" t="n">
         <v>1</v>
@@ -68343,12 +68334,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Farmers and Merchants Trust Company of Chambersburg</t>
+          <t>The Bank of Commerce</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -68360,16 +68351,16 @@
         <v>2.34</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>1.26508929370285</v>
+        <v>2.129422997033723</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1.098972614626358</v>
+        <v>1.347775536702867</v>
       </c>
       <c r="G145" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H145" s="4" t="n">
-        <v>8.829927314414981</v>
+        <v>15.69355733030755</v>
       </c>
       <c r="I145" s="2" t="n">
         <v>1</v>
@@ -68463,12 +68454,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Golden Bank, National Association</t>
+          <t>Plumas Bank</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -68480,16 +68471,16 @@
         <v>2.28</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>1.593490844276205</v>
+        <v>1.79999633674924</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>2.159748510892555</v>
+        <v>1.548422420560316</v>
       </c>
       <c r="G148" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H148" s="4" t="n">
-        <v>13.74226639365613</v>
+        <v>11.76517026369377</v>
       </c>
       <c r="I148" s="2" t="n">
         <v>1</v>
@@ -68503,12 +68494,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Plumas Bank</t>
+          <t>Golden Bank, National Association</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -68520,16 +68511,16 @@
         <v>2.28</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>1.79999633674924</v>
+        <v>1.593490844276205</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>1.548422420560316</v>
+        <v>2.159748510892555</v>
       </c>
       <c r="G149" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H149" s="4" t="n">
-        <v>11.76517026369377</v>
+        <v>13.74226639365613</v>
       </c>
       <c r="I149" s="2" t="n">
         <v>1</v>
@@ -68983,12 +68974,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>First Financial Bank</t>
+          <t>Peoples Bank</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -69000,16 +68991,16 @@
         <v>2.04</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>2.180831437311634</v>
+        <v>0.4310931577664338</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>3.639799841323551</v>
+        <v>1.09969193475077</v>
       </c>
       <c r="G161" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H161" s="4" t="n">
-        <v>11.15053646273767</v>
+        <v>9.314073510405246</v>
       </c>
       <c r="I161" s="2" t="n">
         <v>1</v>
@@ -69023,12 +69014,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Peoples Bank</t>
+          <t>First Financial Bank</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -69040,16 +69031,16 @@
         <v>2.04</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>0.4310931577664338</v>
+        <v>2.180831437311634</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>1.09969193475077</v>
+        <v>3.639799841323551</v>
       </c>
       <c r="G162" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H162" s="4" t="n">
-        <v>9.314073510405246</v>
+        <v>11.15053646273767</v>
       </c>
       <c r="I162" s="2" t="n">
         <v>1</v>
@@ -69423,12 +69414,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Legacy Bank &amp; Trust Company</t>
+          <t>Cornerstone Bank</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ND</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -69440,16 +69431,16 @@
         <v>1.85</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>1.174072608405748</v>
+        <v>1.246445024481687</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>1.466117611692109</v>
+        <v>2.349732423551418</v>
       </c>
       <c r="G172" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H172" s="4" t="n">
-        <v>11.90584030064511</v>
+        <v>9.625572164122522</v>
       </c>
       <c r="I172" s="2" t="n">
         <v>1</v>
@@ -69463,12 +69454,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Cornerstone Bank</t>
+          <t>Bank Of Clarke</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -69480,16 +69471,16 @@
         <v>1.85</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>1.246445024481687</v>
+        <v>1.020126000364984</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>2.349732423551418</v>
+        <v>1.07392091408832</v>
       </c>
       <c r="G173" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H173" s="4" t="n">
-        <v>9.625572164122522</v>
+        <v>12.26527901512793</v>
       </c>
       <c r="I173" s="2" t="n">
         <v>1</v>
@@ -69503,12 +69494,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Bank Of Clarke</t>
+          <t>Legacy Bank &amp; Trust Company</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -69520,16 +69511,16 @@
         <v>1.85</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>1.020126000364984</v>
+        <v>1.174072608405748</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>1.07392091408832</v>
+        <v>1.466117611692109</v>
       </c>
       <c r="G174" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H174" s="4" t="n">
-        <v>12.26527901512793</v>
+        <v>11.90584030064511</v>
       </c>
       <c r="I174" s="2" t="n">
         <v>1</v>
@@ -69663,12 +69654,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>CCFBank National Association</t>
+          <t>North Dallas Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -69680,16 +69671,16 @@
         <v>1.81</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>0.7362782244606263</v>
+        <v>0.4877332918975847</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>2.281858147459817</v>
+        <v>1.542094165465671</v>
       </c>
       <c r="G178" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H178" s="4" t="n">
-        <v>11.21273893144994</v>
+        <v>10.2185142115369</v>
       </c>
       <c r="I178" s="2" t="n">
         <v>1</v>
@@ -69703,12 +69694,12 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>North Dallas Bank &amp; Trust Co.</t>
+          <t>CCFBank National Association</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>WI</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -69720,16 +69711,16 @@
         <v>1.81</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>0.4877332918975847</v>
+        <v>0.7362782244606263</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>1.542094165465671</v>
+        <v>2.281858147459817</v>
       </c>
       <c r="G179" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H179" s="4" t="n">
-        <v>10.2185142115369</v>
+        <v>11.21273893144994</v>
       </c>
       <c r="I179" s="2" t="n">
         <v>1</v>
@@ -70063,12 +70054,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Troy Bank &amp; Trust Company</t>
+          <t>Landmark National Bank</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -70080,16 +70071,16 @@
         <v>1.6</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>1.365026071559052</v>
+        <v>1.331258129898104</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>1.350291647046314</v>
+        <v>1.179909266957297</v>
       </c>
       <c r="G188" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H188" s="4" t="n">
-        <v>12.83068808172287</v>
+        <v>10.16533554399507</v>
       </c>
       <c r="I188" s="2" t="n">
         <v>1</v>
@@ -70143,12 +70134,12 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Landmark National Bank</t>
+          <t>Bankhometown</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -70160,16 +70151,16 @@
         <v>1.6</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>1.331258129898104</v>
+        <v>0.6494980686110394</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>1.179909266957297</v>
+        <v>2.741538511977106</v>
       </c>
       <c r="G190" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H190" s="4" t="n">
-        <v>10.16533554399507</v>
+        <v>11.23995763219953</v>
       </c>
       <c r="I190" s="2" t="n">
         <v>1</v>
@@ -70183,12 +70174,12 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Bankhometown</t>
+          <t>Troy Bank &amp; Trust Company</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -70200,16 +70191,16 @@
         <v>1.6</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>0.6494980686110394</v>
+        <v>1.365026071559052</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>2.741538511977106</v>
+        <v>1.350291647046314</v>
       </c>
       <c r="G191" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H191" s="4" t="n">
-        <v>11.23995763219953</v>
+        <v>12.83068808172287</v>
       </c>
       <c r="I191" s="2" t="n">
         <v>1</v>
@@ -70303,12 +70294,12 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Newburyport Five Cents Savings Bank</t>
+          <t>First Keystone Community Bank</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -70320,16 +70311,16 @@
         <v>1.57</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>0.3880784102464184</v>
+        <v>0.8130186806127812</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>1.662760298254476</v>
+        <v>2.11368460041817</v>
       </c>
       <c r="G194" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H194" s="4" t="n">
-        <v>9.763896122848998</v>
+        <v>9.690011190703498</v>
       </c>
       <c r="I194" s="2" t="n">
         <v>1</v>
@@ -70343,12 +70334,12 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>First Keystone Community Bank</t>
+          <t>Newburyport Five Cents Savings Bank</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -70360,16 +70351,16 @@
         <v>1.57</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>0.8130186806127812</v>
+        <v>0.3880784102464184</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>2.11368460041817</v>
+        <v>1.662760298254476</v>
       </c>
       <c r="G195" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H195" s="4" t="n">
-        <v>9.690011190703498</v>
+        <v>9.763896122848998</v>
       </c>
       <c r="I195" s="2" t="n">
         <v>1</v>
@@ -70503,12 +70494,12 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Dieterich Bank</t>
+          <t>Solera National Bank</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -70520,16 +70511,16 @@
         <v>1.55</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>0.6847731720974196</v>
+        <v>1.712385688312393</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>1.871101475190838</v>
+        <v>1.449842345621521</v>
       </c>
       <c r="G199" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H199" s="4" t="n">
-        <v>8.421269414045854</v>
+        <v>8.626875227033006</v>
       </c>
       <c r="I199" s="2" t="n">
         <v>1</v>
@@ -70543,12 +70534,12 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Solera National Bank</t>
+          <t>Dieterich Bank</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -70560,16 +70551,16 @@
         <v>1.55</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>1.712385688312393</v>
+        <v>0.6847731720974196</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>1.449842345621521</v>
+        <v>1.871101475190838</v>
       </c>
       <c r="G200" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H200" s="4" t="n">
-        <v>8.626875227033006</v>
+        <v>8.421269414045854</v>
       </c>
       <c r="I200" s="2" t="n">
         <v>1</v>
@@ -70703,12 +70694,12 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Union County Savings Bank</t>
+          <t>United Bank</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -70720,35 +70711,35 @@
         <v>1.48</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>-1.449965068088155</v>
+        <v>1.307479710222376</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>0.9081836974060226</v>
+        <v>1.354869729779644</v>
       </c>
       <c r="G204" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H204" s="4" t="n">
-        <v>7.772420811298407</v>
+        <v>15.78710099516341</v>
       </c>
       <c r="I204" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>Negative ROA</t>
+          <t>Noncurrent loans &gt;2x peers</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>United Bank</t>
+          <t>Union County Savings Bank</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -70760,23 +70751,23 @@
         <v>1.48</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>1.307479710222376</v>
+        <v>-1.449965068088155</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>1.354869729779644</v>
+        <v>0.9081836974060226</v>
       </c>
       <c r="G205" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H205" s="4" t="n">
-        <v>15.78710099516341</v>
+        <v>7.772420811298407</v>
       </c>
       <c r="I205" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>Noncurrent loans &gt;2x peers</t>
+          <t>Negative ROA</t>
         </is>
       </c>
     </row>
@@ -70863,12 +70854,12 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Apex Bank</t>
+          <t>Central Bank Illinois</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -70880,16 +70871,16 @@
         <v>1.46</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>2.193299408238219</v>
+        <v>0.975397631413088</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>2.491173220718047</v>
+        <v>1.852544280833368</v>
       </c>
       <c r="G208" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H208" s="4" t="n">
-        <v>14.46441461100635</v>
+        <v>10.39029338992812</v>
       </c>
       <c r="I208" s="2" t="n">
         <v>1</v>
@@ -70903,12 +70894,12 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Central Bank Illinois</t>
+          <t>Apex Bank</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -70920,16 +70911,16 @@
         <v>1.46</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>0.975397631413088</v>
+        <v>2.193299408238219</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>1.852544280833368</v>
+        <v>2.491173220718047</v>
       </c>
       <c r="G209" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H209" s="4" t="n">
-        <v>10.39029338992812</v>
+        <v>14.46441461100635</v>
       </c>
       <c r="I209" s="2" t="n">
         <v>1</v>
@@ -71063,12 +71054,12 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Citizens Bank</t>
+          <t>Armed Forces Bank, National Association</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -71080,16 +71071,16 @@
         <v>1.42</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>1.940879440780607</v>
+        <v>1.700175754794076</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>1.138557505829937</v>
+        <v>1.205524344569288</v>
       </c>
       <c r="G213" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H213" s="4" t="n">
-        <v>12.64584441287705</v>
+        <v>13.92216560619634</v>
       </c>
       <c r="I213" s="2" t="n">
         <v>1</v>
@@ -71103,12 +71094,12 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Armed Forces Bank, National Association</t>
+          <t>Citizens Bank</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -71120,16 +71111,16 @@
         <v>1.42</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>1.700175754794076</v>
+        <v>1.940879440780607</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>1.205524344569288</v>
+        <v>1.138557505829937</v>
       </c>
       <c r="G214" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H214" s="4" t="n">
-        <v>13.92216560619634</v>
+        <v>12.64584441287705</v>
       </c>
       <c r="I214" s="2" t="n">
         <v>1</v>
@@ -71143,12 +71134,12 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>1st Financial Bank USA</t>
+          <t>SULLIVAN BANK</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -71160,16 +71151,16 @@
         <v>1.4</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>0.983084183949169</v>
+        <v>1.12910866798443</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>1.512822980564181</v>
+        <v>1.451943705266635</v>
       </c>
       <c r="G215" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H215" s="4" t="n">
-        <v>16.3370109499175</v>
+        <v>8.754597484350871</v>
       </c>
       <c r="I215" s="2" t="n">
         <v>1</v>
@@ -71183,12 +71174,12 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>SULLIVAN BANK</t>
+          <t>1st Financial Bank USA</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -71200,16 +71191,16 @@
         <v>1.4</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>1.12910866798443</v>
+        <v>0.983084183949169</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>1.451943705266635</v>
+        <v>1.512822980564181</v>
       </c>
       <c r="G216" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H216" s="4" t="n">
-        <v>8.754597484350871</v>
+        <v>16.3370109499175</v>
       </c>
       <c r="I216" s="2" t="n">
         <v>1</v>
@@ -71263,12 +71254,12 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Wallis Bank</t>
+          <t>State Bank of India (California)</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -71280,16 +71271,16 @@
         <v>1.38</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>2.020571216153456</v>
+        <v>1.095267386520152</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>1.426834545355802</v>
+        <v>1.106709409946605</v>
       </c>
       <c r="G218" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H218" s="4" t="n">
-        <v>10.09602281917561</v>
+        <v>14.04850166561888</v>
       </c>
       <c r="I218" s="2" t="n">
         <v>1</v>
@@ -71303,12 +71294,12 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>State Bank of India (California)</t>
+          <t>Wallis Bank</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -71320,16 +71311,16 @@
         <v>1.38</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>1.095267386520152</v>
+        <v>2.020571216153456</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>1.106709409946605</v>
+        <v>1.426834545355802</v>
       </c>
       <c r="G219" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H219" s="4" t="n">
-        <v>14.04850166561888</v>
+        <v>10.09602281917561</v>
       </c>
       <c r="I219" s="2" t="n">
         <v>1</v>
@@ -71383,12 +71374,12 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>County National Bank</t>
+          <t>Century Bank</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -71400,16 +71391,16 @@
         <v>1.36</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>1.000844869045298</v>
+        <v>0.9523179095836437</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>2.622497911269316</v>
+        <v>1.070890108615642</v>
       </c>
       <c r="G221" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H221" s="4" t="n">
-        <v>9.338816532830956</v>
+        <v>10.25184207959749</v>
       </c>
       <c r="I221" s="2" t="n">
         <v>1</v>
@@ -71463,12 +71454,12 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Century Bank</t>
+          <t>County National Bank</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -71480,16 +71471,16 @@
         <v>1.36</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>0.9523179095836437</v>
+        <v>1.000844869045298</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>1.070890108615642</v>
+        <v>2.622497911269316</v>
       </c>
       <c r="G223" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H223" s="4" t="n">
-        <v>10.25184207959749</v>
+        <v>9.338816532830956</v>
       </c>
       <c r="I223" s="2" t="n">
         <v>1</v>
@@ -71543,12 +71534,12 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Sabine State Bank and Trust Company</t>
+          <t>Merchants &amp; Marine Bank</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -71560,16 +71551,16 @@
         <v>1.35</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>1.742372611544182</v>
+        <v>2.221234733242572</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>1.660294443979614</v>
+        <v>1.939328293172134</v>
       </c>
       <c r="G225" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H225" s="4" t="n">
-        <v>8.276582297485035</v>
+        <v>8.832803309092574</v>
       </c>
       <c r="I225" s="2" t="n">
         <v>1</v>
@@ -71583,12 +71574,12 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>InBank</t>
+          <t>Sabine State Bank and Trust Company</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -71600,16 +71591,16 @@
         <v>1.35</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>1.083078995191086</v>
+        <v>1.742372611544182</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>1.311793303977282</v>
+        <v>1.660294443979614</v>
       </c>
       <c r="G226" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H226" s="4" t="n">
-        <v>11.45572928545736</v>
+        <v>8.276582297485035</v>
       </c>
       <c r="I226" s="2" t="n">
         <v>1</v>
@@ -71623,12 +71614,12 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Merchants &amp; Marine Bank</t>
+          <t>InBank</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -71640,16 +71631,16 @@
         <v>1.35</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>2.221234733242572</v>
+        <v>1.083078995191086</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>1.939328293172134</v>
+        <v>1.311793303977282</v>
       </c>
       <c r="G227" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H227" s="4" t="n">
-        <v>8.832803309092574</v>
+        <v>11.45572928545736</v>
       </c>
       <c r="I227" s="2" t="n">
         <v>1</v>
@@ -71783,12 +71774,12 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Plains Commerce Bank</t>
+          <t>Jonesboro State Bank</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -71800,16 +71791,16 @@
         <v>1.3</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>1.337992970073233</v>
+        <v>1.896019305497195</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>1.21553748337628</v>
+        <v>1.643619122876333</v>
       </c>
       <c r="G231" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H231" s="4" t="n">
-        <v>10.0295993134081</v>
+        <v>7.665974711918914</v>
       </c>
       <c r="I231" s="2" t="n">
         <v>1</v>
@@ -71863,12 +71854,12 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Jonesboro State Bank</t>
+          <t>Plains Commerce Bank</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -71880,16 +71871,16 @@
         <v>1.3</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>1.896019305497195</v>
+        <v>1.337992970073233</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>1.643619122876333</v>
+        <v>1.21553748337628</v>
       </c>
       <c r="G233" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H233" s="4" t="n">
-        <v>7.665974711918914</v>
+        <v>10.0295993134081</v>
       </c>
       <c r="I233" s="2" t="n">
         <v>1</v>
@@ -71983,12 +71974,12 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>FIDELITY BANK</t>
+          <t>Dayspring Bank</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -72000,16 +71991,16 @@
         <v>1.23</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>0.127031632849783</v>
+        <v>1.058210250494092</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>1.847738815382945</v>
+        <v>1.729802413914201</v>
       </c>
       <c r="G236" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H236" s="4" t="n">
-        <v>20.31900232233945</v>
+        <v>10.7144471836167</v>
       </c>
       <c r="I236" s="2" t="n">
         <v>1</v>
@@ -72023,12 +72014,12 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Dayspring Bank</t>
+          <t>FIDELITY BANK</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -72040,16 +72031,16 @@
         <v>1.23</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>1.058210250494092</v>
+        <v>0.127031632849783</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>1.729802413914201</v>
+        <v>1.847738815382945</v>
       </c>
       <c r="G237" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H237" s="4" t="n">
-        <v>10.7144471836167</v>
+        <v>20.31900232233945</v>
       </c>
       <c r="I237" s="2" t="n">
         <v>1</v>
@@ -72063,12 +72054,12 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Citizens State Bank</t>
+          <t>First Bankers Trust Company, National Association</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -72080,16 +72071,16 @@
         <v>1.22</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>1.65308781606644</v>
+        <v>0.6789267821828032</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>1.992047593430255</v>
+        <v>1.279115836437378</v>
       </c>
       <c r="G238" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H238" s="4" t="n">
-        <v>12.94870156899756</v>
+        <v>9.995171215491732</v>
       </c>
       <c r="I238" s="2" t="n">
         <v>1</v>
@@ -72103,12 +72094,12 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>MutualOne Bank</t>
+          <t>Citizens State Bank</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -72120,16 +72111,16 @@
         <v>1.22</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>0.8829170441622175</v>
+        <v>1.65308781606644</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>5.919405373574457</v>
+        <v>1.992047593430255</v>
       </c>
       <c r="G239" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H239" s="4" t="n">
-        <v>21.08499357326478</v>
+        <v>12.94870156899756</v>
       </c>
       <c r="I239" s="2" t="n">
         <v>1</v>
@@ -72143,12 +72134,12 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>First Bankers Trust Company, National Association</t>
+          <t>MutualOne Bank</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -72160,16 +72151,16 @@
         <v>1.22</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>0.6789267821828032</v>
+        <v>0.8829170441622175</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>1.279115836437378</v>
+        <v>5.919405373574457</v>
       </c>
       <c r="G240" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H240" s="4" t="n">
-        <v>9.995171215491732</v>
+        <v>21.08499357326478</v>
       </c>
       <c r="I240" s="2" t="n">
         <v>1</v>
@@ -72383,12 +72374,12 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Metro Bank</t>
+          <t>PriorityOne Bank</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -72400,16 +72391,16 @@
         <v>1.18</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>1.412633988558846</v>
+        <v>2.033157683052361</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>1.177971478918872</v>
+        <v>1.580840539758269</v>
       </c>
       <c r="G246" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H246" s="4" t="n">
-        <v>14.68410852062221</v>
+        <v>11.88978819421625</v>
       </c>
       <c r="I246" s="2" t="n">
         <v>1</v>
@@ -72423,12 +72414,12 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>PriorityOne Bank</t>
+          <t>Metro Bank</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -72440,16 +72431,16 @@
         <v>1.18</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>2.033157683052361</v>
+        <v>1.412633988558846</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>1.580840539758269</v>
+        <v>1.177971478918872</v>
       </c>
       <c r="G247" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H247" s="4" t="n">
-        <v>11.88978819421625</v>
+        <v>14.68410852062221</v>
       </c>
       <c r="I247" s="2" t="n">
         <v>1</v>
@@ -72663,12 +72654,12 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>The Evangeline Bank and Trust Company</t>
+          <t>First National Bank, Ames, Iowa</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -72680,16 +72671,16 @@
         <v>1.11</v>
       </c>
       <c r="E253" s="4" t="n">
-        <v>1.794739334838052</v>
+        <v>1.231976324030421</v>
       </c>
       <c r="F253" s="4" t="n">
-        <v>1.243808380812272</v>
+        <v>1.406877496761673</v>
       </c>
       <c r="G253" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H253" s="4" t="n">
-        <v>14.22422377920831</v>
+        <v>9.864433219099881</v>
       </c>
       <c r="I253" s="2" t="n">
         <v>1</v>
@@ -72703,12 +72694,12 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Liberty Savings Bank, F.S.B.</t>
+          <t>St. Louis Bank</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -72720,16 +72711,16 @@
         <v>1.11</v>
       </c>
       <c r="E254" s="4" t="n">
-        <v>0.3630882422885627</v>
+        <v>0.9208712668076099</v>
       </c>
       <c r="F254" s="4" t="n">
-        <v>1.42020190112022</v>
+        <v>2.866832327379008</v>
       </c>
       <c r="G254" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H254" s="4" t="n">
-        <v>9.613861492588665</v>
+        <v>8.810467580179219</v>
       </c>
       <c r="I254" s="2" t="n">
         <v>1</v>
@@ -72743,12 +72734,12 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>St. Louis Bank</t>
+          <t>Bank of Labor</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -72760,16 +72751,16 @@
         <v>1.11</v>
       </c>
       <c r="E255" s="4" t="n">
-        <v>0.9208712668076099</v>
+        <v>0.9098887802012977</v>
       </c>
       <c r="F255" s="4" t="n">
-        <v>2.866832327379008</v>
+        <v>3.148982224457223</v>
       </c>
       <c r="G255" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H255" s="4" t="n">
-        <v>8.810467580179219</v>
+        <v>7.986686557780284</v>
       </c>
       <c r="I255" s="2" t="n">
         <v>1</v>
@@ -72783,12 +72774,12 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Bank of Labor</t>
+          <t>The Evangeline Bank and Trust Company</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -72800,16 +72791,16 @@
         <v>1.11</v>
       </c>
       <c r="E256" s="4" t="n">
-        <v>0.9098887802012977</v>
+        <v>1.794739334838052</v>
       </c>
       <c r="F256" s="4" t="n">
-        <v>3.148982224457223</v>
+        <v>1.243808380812272</v>
       </c>
       <c r="G256" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H256" s="4" t="n">
-        <v>7.986686557780284</v>
+        <v>14.22422377920831</v>
       </c>
       <c r="I256" s="2" t="n">
         <v>1</v>
@@ -72863,12 +72854,12 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>First National Bank, Ames, Iowa</t>
+          <t>Liberty Savings Bank, F.S.B.</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -72880,16 +72871,16 @@
         <v>1.11</v>
       </c>
       <c r="E258" s="4" t="n">
-        <v>1.231976324030421</v>
+        <v>0.3630882422885627</v>
       </c>
       <c r="F258" s="4" t="n">
-        <v>1.406877496761673</v>
+        <v>1.42020190112022</v>
       </c>
       <c r="G258" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H258" s="4" t="n">
-        <v>9.864433219099881</v>
+        <v>9.613861492588665</v>
       </c>
       <c r="I258" s="2" t="n">
         <v>1</v>
@@ -72943,12 +72934,12 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Pioneer Bank</t>
+          <t>Generations Bank</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -72960,16 +72951,16 @@
         <v>1.09</v>
       </c>
       <c r="E260" s="4" t="n">
-        <v>2.584451053423047</v>
+        <v>1.193588459251441</v>
       </c>
       <c r="F260" s="4" t="n">
-        <v>1.713686081117447</v>
+        <v>1.505403275882761</v>
       </c>
       <c r="G260" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H260" s="4" t="n">
-        <v>12.31683734673634</v>
+        <v>11.51487194324723</v>
       </c>
       <c r="I260" s="2" t="n">
         <v>1</v>
@@ -72983,12 +72974,12 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Prime Alliance Bank</t>
+          <t>Pioneer Bank</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -73000,16 +72991,16 @@
         <v>1.09</v>
       </c>
       <c r="E261" s="4" t="n">
-        <v>3.406717436871994</v>
+        <v>2.584451053423047</v>
       </c>
       <c r="F261" s="4" t="n">
-        <v>1.598428376090416</v>
+        <v>1.713686081117447</v>
       </c>
       <c r="G261" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H261" s="4" t="n">
-        <v>11.52991071678573</v>
+        <v>12.31683734673634</v>
       </c>
       <c r="I261" s="2" t="n">
         <v>1</v>
@@ -73023,12 +73014,12 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Generations Bank</t>
+          <t>Prime Alliance Bank</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -73040,16 +73031,16 @@
         <v>1.09</v>
       </c>
       <c r="E262" s="4" t="n">
-        <v>1.193588459251441</v>
+        <v>3.406717436871994</v>
       </c>
       <c r="F262" s="4" t="n">
-        <v>1.505403275882761</v>
+        <v>1.598428376090416</v>
       </c>
       <c r="G262" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H262" s="4" t="n">
-        <v>11.51487194324723</v>
+        <v>11.52991071678573</v>
       </c>
       <c r="I262" s="2" t="n">
         <v>1</v>
@@ -73103,12 +73094,12 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>MountainOne Bank</t>
+          <t>The Federal Savings Bank</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -73120,16 +73111,16 @@
         <v>1.08</v>
       </c>
       <c r="E264" s="4" t="n">
-        <v>1.216161755011887</v>
+        <v>0.05289834276180423</v>
       </c>
       <c r="F264" s="4" t="n">
-        <v>1.055384060127373</v>
+        <v>2.692323182046773</v>
       </c>
       <c r="G264" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H264" s="4" t="n">
-        <v>14.74544903112039</v>
+        <v>15.85592073571901</v>
       </c>
       <c r="I264" s="2" t="n">
         <v>1</v>
@@ -73143,12 +73134,12 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>The First National Bank of Bemidji</t>
+          <t>MountainOne Bank</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -73160,16 +73151,16 @@
         <v>1.08</v>
       </c>
       <c r="E265" s="4" t="n">
-        <v>1.422082529240563</v>
+        <v>1.216161755011887</v>
       </c>
       <c r="F265" s="4" t="n">
-        <v>1.990970185572347</v>
+        <v>1.055384060127373</v>
       </c>
       <c r="G265" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H265" s="4" t="n">
-        <v>11.14102017893799</v>
+        <v>14.74544903112039</v>
       </c>
       <c r="I265" s="2" t="n">
         <v>1</v>
@@ -73183,12 +73174,12 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>The Federal Savings Bank</t>
+          <t>The First National Bank of McGregor</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -73200,16 +73191,16 @@
         <v>1.08</v>
       </c>
       <c r="E266" s="4" t="n">
-        <v>0.05289834276180423</v>
+        <v>1.089600776426695</v>
       </c>
       <c r="F266" s="4" t="n">
-        <v>2.692323182046773</v>
+        <v>2.723311546840959</v>
       </c>
       <c r="G266" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H266" s="4" t="n">
-        <v>15.85592073571901</v>
+        <v>9.54590438824984</v>
       </c>
       <c r="I266" s="2" t="n">
         <v>1</v>
@@ -73223,12 +73214,12 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>The First National Bank of McGregor</t>
+          <t>The First National Bank of Bemidji</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -73240,16 +73231,16 @@
         <v>1.08</v>
       </c>
       <c r="E267" s="4" t="n">
-        <v>1.089600776426695</v>
+        <v>1.422082529240563</v>
       </c>
       <c r="F267" s="4" t="n">
-        <v>2.723311546840959</v>
+        <v>1.990970185572347</v>
       </c>
       <c r="G267" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H267" s="4" t="n">
-        <v>9.54590438824984</v>
+        <v>11.14102017893799</v>
       </c>
       <c r="I267" s="2" t="n">
         <v>1</v>
@@ -73263,12 +73254,12 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>Crescent Bank</t>
+          <t>Brooks Bank, National Association</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -73280,16 +73271,16 @@
         <v>1.07</v>
       </c>
       <c r="E268" s="4" t="n">
-        <v>8.336080647785522</v>
+        <v>2.098607629262268</v>
       </c>
       <c r="F268" s="4" t="n">
-        <v>1.279446925552214</v>
+        <v>2.610187757722602</v>
       </c>
       <c r="G268" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H268" s="4" t="n">
-        <v>15.00955363586999</v>
+        <v>13.31243367136372</v>
       </c>
       <c r="I268" s="2" t="n">
         <v>1</v>
@@ -73303,12 +73294,12 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>Brooks Bank, National Association</t>
+          <t>Crescent Bank</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -73320,16 +73311,16 @@
         <v>1.07</v>
       </c>
       <c r="E269" s="4" t="n">
-        <v>2.098607629262268</v>
+        <v>8.336080647785522</v>
       </c>
       <c r="F269" s="4" t="n">
-        <v>2.610187757722602</v>
+        <v>1.279446925552214</v>
       </c>
       <c r="G269" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H269" s="4" t="n">
-        <v>13.31243367136372</v>
+        <v>15.00955363586999</v>
       </c>
       <c r="I269" s="2" t="n">
         <v>1</v>
@@ -73343,12 +73334,12 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CommerceOne Bank</t>
+          <t>Centennial Bank</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -73360,35 +73351,35 @@
         <v>1.06</v>
       </c>
       <c r="E270" s="4" t="n">
-        <v>-0.1614620907623072</v>
+        <v>0.9840674789128397</v>
       </c>
       <c r="F270" s="4" t="n">
-        <v>0</v>
+        <v>1.259846509122521</v>
       </c>
       <c r="G270" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H270" s="4" t="n">
-        <v>9.014557555189484</v>
+        <v>9.821456398245259</v>
       </c>
       <c r="I270" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>Negative ROA</t>
+          <t>Noncurrent loans &gt;2x peers</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>Border Bank</t>
+          <t>CommerceOne Bank</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -73400,35 +73391,35 @@
         <v>1.06</v>
       </c>
       <c r="E271" s="4" t="n">
-        <v>1.306148684890688</v>
+        <v>-0.1614620907623072</v>
       </c>
       <c r="F271" s="4" t="n">
-        <v>1.068984259741989</v>
+        <v>0</v>
       </c>
       <c r="G271" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H271" s="4" t="n">
-        <v>9.070499606461526</v>
+        <v>9.014557555189484</v>
       </c>
       <c r="I271" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>Noncurrent loans &gt;2x peers</t>
+          <t>Negative ROA</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>Centennial Bank</t>
+          <t>Border Bank</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>ND</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -73440,16 +73431,16 @@
         <v>1.06</v>
       </c>
       <c r="E272" s="4" t="n">
-        <v>0.9840674789128397</v>
+        <v>1.306148684890688</v>
       </c>
       <c r="F272" s="4" t="n">
-        <v>1.259846509122521</v>
+        <v>1.068984259741989</v>
       </c>
       <c r="G272" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H272" s="4" t="n">
-        <v>9.821456398245259</v>
+        <v>9.070499606461526</v>
       </c>
       <c r="I272" s="2" t="n">
         <v>1</v>
@@ -73503,12 +73494,12 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>Security Financial Bank</t>
+          <t>First Southern Bank</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -73520,16 +73511,16 @@
         <v>1.04</v>
       </c>
       <c r="E274" s="4" t="n">
-        <v>1.636803755020379</v>
+        <v>1.370978025043838</v>
       </c>
       <c r="F274" s="4" t="n">
-        <v>1.437797259767931</v>
+        <v>2.997180039744816</v>
       </c>
       <c r="G274" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H274" s="4" t="n">
-        <v>9.668487571889223</v>
+        <v>10.8528880866426</v>
       </c>
       <c r="I274" s="2" t="n">
         <v>1</v>
@@ -73543,12 +73534,12 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>The Freedom Bank of Virginia</t>
+          <t>Security Financial Bank</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>WI</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -73560,16 +73551,16 @@
         <v>1.04</v>
       </c>
       <c r="E275" s="4" t="n">
-        <v>0.4453720121454717</v>
+        <v>1.636803755020379</v>
       </c>
       <c r="F275" s="4" t="n">
-        <v>3.263774737161629</v>
+        <v>1.437797259767931</v>
       </c>
       <c r="G275" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H275" s="4" t="n">
-        <v>11.05912662922399</v>
+        <v>9.668487571889223</v>
       </c>
       <c r="I275" s="2" t="n">
         <v>1</v>
@@ -73583,12 +73574,12 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>First Southern Bank</t>
+          <t>The Freedom Bank of Virginia</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -73600,16 +73591,16 @@
         <v>1.04</v>
       </c>
       <c r="E276" s="4" t="n">
-        <v>1.370978025043838</v>
+        <v>0.4453720121454717</v>
       </c>
       <c r="F276" s="4" t="n">
-        <v>2.997180039744816</v>
+        <v>3.263774737161629</v>
       </c>
       <c r="G276" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H276" s="4" t="n">
-        <v>10.8528880866426</v>
+        <v>11.05912662922399</v>
       </c>
       <c r="I276" s="2" t="n">
         <v>1</v>
@@ -73623,12 +73614,12 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>First Central Savings Bank</t>
+          <t>R Bank</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -73640,16 +73631,16 @@
         <v>1.03</v>
       </c>
       <c r="E277" s="4" t="n">
-        <v>0.9711513509471805</v>
+        <v>0.7242130472999656</v>
       </c>
       <c r="F277" s="4" t="n">
-        <v>1.186253786213162</v>
+        <v>1.545392246951267</v>
       </c>
       <c r="G277" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H277" s="4" t="n">
-        <v>10.29878388484298</v>
+        <v>9.010771074647959</v>
       </c>
       <c r="I277" s="2" t="n">
         <v>1</v>
@@ -73663,12 +73654,12 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>R Bank</t>
+          <t>First Central Savings Bank</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -73680,16 +73671,16 @@
         <v>1.03</v>
       </c>
       <c r="E278" s="4" t="n">
-        <v>0.7242130472999656</v>
+        <v>0.9711513509471805</v>
       </c>
       <c r="F278" s="4" t="n">
-        <v>1.545392246951267</v>
+        <v>1.186253786213162</v>
       </c>
       <c r="G278" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H278" s="4" t="n">
-        <v>9.010771074647959</v>
+        <v>10.29878388484298</v>
       </c>
       <c r="I278" s="2" t="n">
         <v>1</v>
@@ -73743,12 +73734,12 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>Adirondack Bank</t>
+          <t>Presidential Bank, FSB</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -73760,35 +73751,35 @@
         <v>1.01</v>
       </c>
       <c r="E280" s="4" t="n">
-        <v>-2.117984097366266</v>
+        <v>0.4885664705326675</v>
       </c>
       <c r="F280" s="4" t="n">
-        <v>0.7193593555382608</v>
+        <v>1.638145180026194</v>
       </c>
       <c r="G280" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H280" s="4" t="n">
-        <v>7.251912668945216</v>
+        <v>9.633832027867829</v>
       </c>
       <c r="I280" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>Negative ROA</t>
+          <t>Noncurrent loans &gt;2x peers</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Presidential Bank, FSB</t>
+          <t>Adirondack Bank</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -73800,23 +73791,23 @@
         <v>1.01</v>
       </c>
       <c r="E281" s="4" t="n">
-        <v>0.4885664705326675</v>
+        <v>-2.117984097366266</v>
       </c>
       <c r="F281" s="4" t="n">
-        <v>1.638145180026194</v>
+        <v>0.7193593555382608</v>
       </c>
       <c r="G281" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H281" s="4" t="n">
-        <v>9.633832027867829</v>
+        <v>7.251912668945216</v>
       </c>
       <c r="I281" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>Noncurrent loans &gt;2x peers</t>
+          <t>Negative ROA</t>
         </is>
       </c>
     </row>

--- a/outputs/bank_peer_report.xlsx
+++ b/outputs/bank_peer_report.xlsx
@@ -24731,7 +24731,7 @@
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>The Bank of Greene</t>
+          <t>Bank of Greene</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -67094,12 +67094,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Industrial and Commercial Bank of China USA, National Association</t>
+          <t>BayCoast Bank</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -67111,16 +67111,16 @@
         <v>2.86</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>0.6656889350773629</v>
+        <v>0.5090433189373119</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>4.20456752393268</v>
+        <v>1.454210849955982</v>
       </c>
       <c r="G114" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>17.25538300510983</v>
+        <v>8.291879818761434</v>
       </c>
       <c r="I114" s="2" t="n">
         <v>1</v>
@@ -67134,12 +67134,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>BayCoast Bank</t>
+          <t>Industrial and Commercial Bank of China USA, National Association</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -67151,16 +67151,16 @@
         <v>2.86</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>0.5090433189373119</v>
+        <v>0.6656889350773629</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1.454210849955982</v>
+        <v>4.20456752393268</v>
       </c>
       <c r="G115" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>8.291879818761434</v>
+        <v>17.25538300510983</v>
       </c>
       <c r="I115" s="2" t="n">
         <v>1</v>
@@ -67654,12 +67654,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Dedham Institution for Savings</t>
+          <t>Fidelity Bank &amp; Trust</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -67671,16 +67671,16 @@
         <v>2.6</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>0.8805319205415725</v>
+        <v>1.299257276220965</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1.151368008217387</v>
+        <v>1.262121833628537</v>
       </c>
       <c r="G128" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>11.39483162870477</v>
+        <v>8.977787431003502</v>
       </c>
       <c r="I128" s="2" t="n">
         <v>1</v>
@@ -67694,12 +67694,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Fidelity Bank &amp; Trust</t>
+          <t>KS StateBank</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -67711,16 +67711,16 @@
         <v>2.6</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>1.299257276220965</v>
+        <v>1.949015717547198</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1.262121833628537</v>
+        <v>2.493799528159216</v>
       </c>
       <c r="G129" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H129" s="4" t="n">
-        <v>8.977787431003502</v>
+        <v>12.96524297547413</v>
       </c>
       <c r="I129" s="2" t="n">
         <v>1</v>
@@ -67734,12 +67734,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>KS StateBank</t>
+          <t>Dedham Institution for Savings</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -67751,16 +67751,16 @@
         <v>2.6</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>1.949015717547198</v>
+        <v>0.8805319205415725</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>2.493799528159216</v>
+        <v>1.151368008217387</v>
       </c>
       <c r="G130" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>12.96524297547413</v>
+        <v>11.39483162870477</v>
       </c>
       <c r="I130" s="2" t="n">
         <v>1</v>
@@ -67774,7 +67774,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>State Bank of Texas</t>
+          <t>Wells Fargo Bank South Central, National Association</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -67791,16 +67791,16 @@
         <v>2.59</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>4.240736806108307</v>
+        <v>1.621537596044236</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>2.15529406371281</v>
+        <v>1.238147618009484</v>
       </c>
       <c r="G131" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H131" s="4" t="n">
-        <v>15.70547302422191</v>
+        <v>29.69171119921634</v>
       </c>
       <c r="I131" s="2" t="n">
         <v>1</v>
@@ -67814,7 +67814,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Wells Fargo Bank South Central, National Association</t>
+          <t>State Bank of Texas</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -67831,16 +67831,16 @@
         <v>2.59</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>1.621537596044236</v>
+        <v>4.240736806108307</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1.238147618009484</v>
+        <v>2.15529406371281</v>
       </c>
       <c r="G132" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>29.69171119921634</v>
+        <v>15.70547302422191</v>
       </c>
       <c r="I132" s="2" t="n">
         <v>1</v>
@@ -67974,12 +67974,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Newtek Bank, National Association</t>
+          <t>Somerset Trust Company</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -67991,16 +67991,16 @@
         <v>2.47</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>4.402542597877482</v>
+        <v>1.157529144178948</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>7.185663489314225</v>
+        <v>1.494812595623905</v>
       </c>
       <c r="G136" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>8.610542311625865</v>
+        <v>9.100596879444391</v>
       </c>
       <c r="I136" s="2" t="n">
         <v>1</v>
@@ -68014,12 +68014,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Somerset Trust Company</t>
+          <t>Newtek Bank, National Association</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -68031,16 +68031,16 @@
         <v>2.47</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>1.157529144178948</v>
+        <v>4.402542597877482</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1.494812595623905</v>
+        <v>7.185663489314225</v>
       </c>
       <c r="G137" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>9.100596879444391</v>
+        <v>8.610542311625865</v>
       </c>
       <c r="I137" s="2" t="n">
         <v>1</v>
@@ -68254,12 +68254,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Farmers and Merchants Trust Company of Chambersburg</t>
+          <t>First Bank of the Lake</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -68271,16 +68271,16 @@
         <v>2.34</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>1.26508929370285</v>
+        <v>0.8303325529933406</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1.098972614626358</v>
+        <v>3.699320495437402</v>
       </c>
       <c r="G143" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>8.829927314414981</v>
+        <v>7.083360361621424</v>
       </c>
       <c r="I143" s="2" t="n">
         <v>1</v>
@@ -68294,12 +68294,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>First Bank of the Lake</t>
+          <t>The Bank of Commerce</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -68311,16 +68311,16 @@
         <v>2.34</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>0.8303325529933406</v>
+        <v>2.129422997033723</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>3.699320495437402</v>
+        <v>1.347775536702867</v>
       </c>
       <c r="G144" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H144" s="4" t="n">
-        <v>7.083360361621424</v>
+        <v>15.69355733030755</v>
       </c>
       <c r="I144" s="2" t="n">
         <v>1</v>
@@ -68334,12 +68334,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>The Bank of Commerce</t>
+          <t>Farmers and Merchants Trust Company of Chambersburg</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -68351,16 +68351,16 @@
         <v>2.34</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>2.129422997033723</v>
+        <v>1.26508929370285</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1.347775536702867</v>
+        <v>1.098972614626358</v>
       </c>
       <c r="G145" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H145" s="4" t="n">
-        <v>15.69355733030755</v>
+        <v>8.829927314414981</v>
       </c>
       <c r="I145" s="2" t="n">
         <v>1</v>
@@ -68454,12 +68454,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Plumas Bank</t>
+          <t>Golden Bank, National Association</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -68471,16 +68471,16 @@
         <v>2.28</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>1.79999633674924</v>
+        <v>1.593490844276205</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>1.548422420560316</v>
+        <v>2.159748510892555</v>
       </c>
       <c r="G148" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H148" s="4" t="n">
-        <v>11.76517026369377</v>
+        <v>13.74226639365613</v>
       </c>
       <c r="I148" s="2" t="n">
         <v>1</v>
@@ -68494,12 +68494,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Golden Bank, National Association</t>
+          <t>Plumas Bank</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -68511,16 +68511,16 @@
         <v>2.28</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>1.593490844276205</v>
+        <v>1.79999633674924</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>2.159748510892555</v>
+        <v>1.548422420560316</v>
       </c>
       <c r="G149" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H149" s="4" t="n">
-        <v>13.74226639365613</v>
+        <v>11.76517026369377</v>
       </c>
       <c r="I149" s="2" t="n">
         <v>1</v>
@@ -68974,12 +68974,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Peoples Bank</t>
+          <t>First Financial Bank</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -68991,16 +68991,16 @@
         <v>2.04</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>0.4310931577664338</v>
+        <v>2.180831437311634</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>1.09969193475077</v>
+        <v>3.639799841323551</v>
       </c>
       <c r="G161" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H161" s="4" t="n">
-        <v>9.314073510405246</v>
+        <v>11.15053646273767</v>
       </c>
       <c r="I161" s="2" t="n">
         <v>1</v>
@@ -69014,12 +69014,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>First Financial Bank</t>
+          <t>Peoples Bank</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -69031,16 +69031,16 @@
         <v>2.04</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>2.180831437311634</v>
+        <v>0.4310931577664338</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>3.639799841323551</v>
+        <v>1.09969193475077</v>
       </c>
       <c r="G162" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H162" s="4" t="n">
-        <v>11.15053646273767</v>
+        <v>9.314073510405246</v>
       </c>
       <c r="I162" s="2" t="n">
         <v>1</v>
@@ -69414,12 +69414,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Cornerstone Bank</t>
+          <t>Legacy Bank &amp; Trust Company</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -69431,16 +69431,16 @@
         <v>1.85</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>1.246445024481687</v>
+        <v>1.174072608405748</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>2.349732423551418</v>
+        <v>1.466117611692109</v>
       </c>
       <c r="G172" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H172" s="4" t="n">
-        <v>9.625572164122522</v>
+        <v>11.90584030064511</v>
       </c>
       <c r="I172" s="2" t="n">
         <v>1</v>
@@ -69454,12 +69454,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Bank Of Clarke</t>
+          <t>Cornerstone Bank</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>ND</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -69471,16 +69471,16 @@
         <v>1.85</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>1.020126000364984</v>
+        <v>1.246445024481687</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>1.07392091408832</v>
+        <v>2.349732423551418</v>
       </c>
       <c r="G173" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H173" s="4" t="n">
-        <v>12.26527901512793</v>
+        <v>9.625572164122522</v>
       </c>
       <c r="I173" s="2" t="n">
         <v>1</v>
@@ -69494,12 +69494,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Legacy Bank &amp; Trust Company</t>
+          <t>Bank Of Clarke</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -69511,16 +69511,16 @@
         <v>1.85</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>1.174072608405748</v>
+        <v>1.020126000364984</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>1.466117611692109</v>
+        <v>1.07392091408832</v>
       </c>
       <c r="G174" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H174" s="4" t="n">
-        <v>11.90584030064511</v>
+        <v>12.26527901512793</v>
       </c>
       <c r="I174" s="2" t="n">
         <v>1</v>
@@ -69654,12 +69654,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>North Dallas Bank &amp; Trust Co.</t>
+          <t>CCFBank National Association</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>WI</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -69671,16 +69671,16 @@
         <v>1.81</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>0.4877332918975847</v>
+        <v>0.7362782244606263</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>1.542094165465671</v>
+        <v>2.281858147459817</v>
       </c>
       <c r="G178" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H178" s="4" t="n">
-        <v>10.2185142115369</v>
+        <v>11.21273893144994</v>
       </c>
       <c r="I178" s="2" t="n">
         <v>1</v>
@@ -69694,12 +69694,12 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>CCFBank National Association</t>
+          <t>North Dallas Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -69711,16 +69711,16 @@
         <v>1.81</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>0.7362782244606263</v>
+        <v>0.4877332918975847</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>2.281858147459817</v>
+        <v>1.542094165465671</v>
       </c>
       <c r="G179" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H179" s="4" t="n">
-        <v>11.21273893144994</v>
+        <v>10.2185142115369</v>
       </c>
       <c r="I179" s="2" t="n">
         <v>1</v>
@@ -70054,12 +70054,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Landmark National Bank</t>
+          <t>Troy Bank &amp; Trust Company</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -70071,16 +70071,16 @@
         <v>1.6</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>1.331258129898104</v>
+        <v>1.365026071559052</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>1.179909266957297</v>
+        <v>1.350291647046314</v>
       </c>
       <c r="G188" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H188" s="4" t="n">
-        <v>10.16533554399507</v>
+        <v>12.83068808172287</v>
       </c>
       <c r="I188" s="2" t="n">
         <v>1</v>
@@ -70134,12 +70134,12 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Bankhometown</t>
+          <t>Landmark National Bank</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -70151,16 +70151,16 @@
         <v>1.6</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>0.6494980686110394</v>
+        <v>1.331258129898104</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>2.741538511977106</v>
+        <v>1.179909266957297</v>
       </c>
       <c r="G190" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H190" s="4" t="n">
-        <v>11.23995763219953</v>
+        <v>10.16533554399507</v>
       </c>
       <c r="I190" s="2" t="n">
         <v>1</v>
@@ -70174,12 +70174,12 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Troy Bank &amp; Trust Company</t>
+          <t>Bankhometown</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -70191,16 +70191,16 @@
         <v>1.6</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>1.365026071559052</v>
+        <v>0.6494980686110394</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>1.350291647046314</v>
+        <v>2.741538511977106</v>
       </c>
       <c r="G191" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H191" s="4" t="n">
-        <v>12.83068808172287</v>
+        <v>11.23995763219953</v>
       </c>
       <c r="I191" s="2" t="n">
         <v>1</v>
@@ -70294,12 +70294,12 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>First Keystone Community Bank</t>
+          <t>Newburyport Five Cents Savings Bank</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -70311,16 +70311,16 @@
         <v>1.57</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>0.8130186806127812</v>
+        <v>0.3880784102464184</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>2.11368460041817</v>
+        <v>1.662760298254476</v>
       </c>
       <c r="G194" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H194" s="4" t="n">
-        <v>9.690011190703498</v>
+        <v>9.763896122848998</v>
       </c>
       <c r="I194" s="2" t="n">
         <v>1</v>
@@ -70334,12 +70334,12 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Newburyport Five Cents Savings Bank</t>
+          <t>First Keystone Community Bank</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -70351,16 +70351,16 @@
         <v>1.57</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>0.3880784102464184</v>
+        <v>0.8130186806127812</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>1.662760298254476</v>
+        <v>2.11368460041817</v>
       </c>
       <c r="G195" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H195" s="4" t="n">
-        <v>9.763896122848998</v>
+        <v>9.690011190703498</v>
       </c>
       <c r="I195" s="2" t="n">
         <v>1</v>
@@ -70494,12 +70494,12 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Solera National Bank</t>
+          <t>Dieterich Bank</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -70511,16 +70511,16 @@
         <v>1.55</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>1.712385688312393</v>
+        <v>0.6847731720974196</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>1.449842345621521</v>
+        <v>1.871101475190838</v>
       </c>
       <c r="G199" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H199" s="4" t="n">
-        <v>8.626875227033006</v>
+        <v>8.421269414045854</v>
       </c>
       <c r="I199" s="2" t="n">
         <v>1</v>
@@ -70534,12 +70534,12 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Dieterich Bank</t>
+          <t>Solera National Bank</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -70551,16 +70551,16 @@
         <v>1.55</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>0.6847731720974196</v>
+        <v>1.712385688312393</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>1.871101475190838</v>
+        <v>1.449842345621521</v>
       </c>
       <c r="G200" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H200" s="4" t="n">
-        <v>8.421269414045854</v>
+        <v>8.626875227033006</v>
       </c>
       <c r="I200" s="2" t="n">
         <v>1</v>
@@ -70694,12 +70694,12 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>United Bank</t>
+          <t>Union County Savings Bank</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -70711,35 +70711,35 @@
         <v>1.48</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>1.307479710222376</v>
+        <v>-1.449965068088155</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>1.354869729779644</v>
+        <v>0.9081836974060226</v>
       </c>
       <c r="G204" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H204" s="4" t="n">
-        <v>15.78710099516341</v>
+        <v>7.772420811298407</v>
       </c>
       <c r="I204" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>Noncurrent loans &gt;2x peers</t>
+          <t>Negative ROA</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Union County Savings Bank</t>
+          <t>United Bank</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -70751,23 +70751,23 @@
         <v>1.48</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>-1.449965068088155</v>
+        <v>1.307479710222376</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>0.9081836974060226</v>
+        <v>1.354869729779644</v>
       </c>
       <c r="G205" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H205" s="4" t="n">
-        <v>7.772420811298407</v>
+        <v>15.78710099516341</v>
       </c>
       <c r="I205" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>Negative ROA</t>
+          <t>Noncurrent loans &gt;2x peers</t>
         </is>
       </c>
     </row>
@@ -70854,12 +70854,12 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Central Bank Illinois</t>
+          <t>Apex Bank</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -70871,16 +70871,16 @@
         <v>1.46</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>0.975397631413088</v>
+        <v>2.193299408238219</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>1.852544280833368</v>
+        <v>2.491173220718047</v>
       </c>
       <c r="G208" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H208" s="4" t="n">
-        <v>10.39029338992812</v>
+        <v>14.46441461100635</v>
       </c>
       <c r="I208" s="2" t="n">
         <v>1</v>
@@ -70894,12 +70894,12 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Apex Bank</t>
+          <t>Central Bank Illinois</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -70911,16 +70911,16 @@
         <v>1.46</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>2.193299408238219</v>
+        <v>0.975397631413088</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>2.491173220718047</v>
+        <v>1.852544280833368</v>
       </c>
       <c r="G209" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H209" s="4" t="n">
-        <v>14.46441461100635</v>
+        <v>10.39029338992812</v>
       </c>
       <c r="I209" s="2" t="n">
         <v>1</v>
@@ -71054,12 +71054,12 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Armed Forces Bank, National Association</t>
+          <t>Citizens Bank</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -71071,16 +71071,16 @@
         <v>1.42</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>1.700175754794076</v>
+        <v>1.940879440780607</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>1.205524344569288</v>
+        <v>1.138557505829937</v>
       </c>
       <c r="G213" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H213" s="4" t="n">
-        <v>13.92216560619634</v>
+        <v>12.64584441287705</v>
       </c>
       <c r="I213" s="2" t="n">
         <v>1</v>
@@ -71094,12 +71094,12 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Citizens Bank</t>
+          <t>Armed Forces Bank, National Association</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -71111,16 +71111,16 @@
         <v>1.42</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>1.940879440780607</v>
+        <v>1.700175754794076</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>1.138557505829937</v>
+        <v>1.205524344569288</v>
       </c>
       <c r="G214" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H214" s="4" t="n">
-        <v>12.64584441287705</v>
+        <v>13.92216560619634</v>
       </c>
       <c r="I214" s="2" t="n">
         <v>1</v>
@@ -71134,12 +71134,12 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>SULLIVAN BANK</t>
+          <t>1st Financial Bank USA</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -71151,16 +71151,16 @@
         <v>1.4</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>1.12910866798443</v>
+        <v>0.983084183949169</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>1.451943705266635</v>
+        <v>1.512822980564181</v>
       </c>
       <c r="G215" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H215" s="4" t="n">
-        <v>8.754597484350871</v>
+        <v>16.3370109499175</v>
       </c>
       <c r="I215" s="2" t="n">
         <v>1</v>
@@ -71174,12 +71174,12 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>1st Financial Bank USA</t>
+          <t>SULLIVAN BANK</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -71191,16 +71191,16 @@
         <v>1.4</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>0.983084183949169</v>
+        <v>1.12910866798443</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>1.512822980564181</v>
+        <v>1.451943705266635</v>
       </c>
       <c r="G216" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H216" s="4" t="n">
-        <v>16.3370109499175</v>
+        <v>8.754597484350871</v>
       </c>
       <c r="I216" s="2" t="n">
         <v>1</v>
@@ -71254,12 +71254,12 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>State Bank of India (California)</t>
+          <t>Wallis Bank</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -71271,16 +71271,16 @@
         <v>1.38</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>1.095267386520152</v>
+        <v>2.020571216153456</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>1.106709409946605</v>
+        <v>1.426834545355802</v>
       </c>
       <c r="G218" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H218" s="4" t="n">
-        <v>14.04850166561888</v>
+        <v>10.09602281917561</v>
       </c>
       <c r="I218" s="2" t="n">
         <v>1</v>
@@ -71294,12 +71294,12 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Wallis Bank</t>
+          <t>State Bank of India (California)</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -71311,16 +71311,16 @@
         <v>1.38</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>2.020571216153456</v>
+        <v>1.095267386520152</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>1.426834545355802</v>
+        <v>1.106709409946605</v>
       </c>
       <c r="G219" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H219" s="4" t="n">
-        <v>10.09602281917561</v>
+        <v>14.04850166561888</v>
       </c>
       <c r="I219" s="2" t="n">
         <v>1</v>
@@ -71374,12 +71374,12 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Century Bank</t>
+          <t>County National Bank</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -71391,16 +71391,16 @@
         <v>1.36</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>0.9523179095836437</v>
+        <v>1.000844869045298</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>1.070890108615642</v>
+        <v>2.622497911269316</v>
       </c>
       <c r="G221" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H221" s="4" t="n">
-        <v>10.25184207959749</v>
+        <v>9.338816532830956</v>
       </c>
       <c r="I221" s="2" t="n">
         <v>1</v>
@@ -71454,12 +71454,12 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>County National Bank</t>
+          <t>Century Bank</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -71471,16 +71471,16 @@
         <v>1.36</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>1.000844869045298</v>
+        <v>0.9523179095836437</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>2.622497911269316</v>
+        <v>1.070890108615642</v>
       </c>
       <c r="G223" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H223" s="4" t="n">
-        <v>9.338816532830956</v>
+        <v>10.25184207959749</v>
       </c>
       <c r="I223" s="2" t="n">
         <v>1</v>
@@ -71534,12 +71534,12 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Merchants &amp; Marine Bank</t>
+          <t>Sabine State Bank and Trust Company</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -71551,16 +71551,16 @@
         <v>1.35</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>2.221234733242572</v>
+        <v>1.742372611544182</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>1.939328293172134</v>
+        <v>1.660294443979614</v>
       </c>
       <c r="G225" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H225" s="4" t="n">
-        <v>8.832803309092574</v>
+        <v>8.276582297485035</v>
       </c>
       <c r="I225" s="2" t="n">
         <v>1</v>
@@ -71574,12 +71574,12 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Sabine State Bank and Trust Company</t>
+          <t>InBank</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -71591,16 +71591,16 @@
         <v>1.35</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>1.742372611544182</v>
+        <v>1.083078995191086</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>1.660294443979614</v>
+        <v>1.311793303977282</v>
       </c>
       <c r="G226" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H226" s="4" t="n">
-        <v>8.276582297485035</v>
+        <v>11.45572928545736</v>
       </c>
       <c r="I226" s="2" t="n">
         <v>1</v>
@@ -71614,12 +71614,12 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>InBank</t>
+          <t>Merchants &amp; Marine Bank</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -71631,16 +71631,16 @@
         <v>1.35</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>1.083078995191086</v>
+        <v>2.221234733242572</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>1.311793303977282</v>
+        <v>1.939328293172134</v>
       </c>
       <c r="G227" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H227" s="4" t="n">
-        <v>11.45572928545736</v>
+        <v>8.832803309092574</v>
       </c>
       <c r="I227" s="2" t="n">
         <v>1</v>
@@ -71774,12 +71774,12 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Jonesboro State Bank</t>
+          <t>Plains Commerce Bank</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -71791,16 +71791,16 @@
         <v>1.3</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>1.896019305497195</v>
+        <v>1.337992970073233</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>1.643619122876333</v>
+        <v>1.21553748337628</v>
       </c>
       <c r="G231" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H231" s="4" t="n">
-        <v>7.665974711918914</v>
+        <v>10.0295993134081</v>
       </c>
       <c r="I231" s="2" t="n">
         <v>1</v>
@@ -71854,12 +71854,12 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Plains Commerce Bank</t>
+          <t>Jonesboro State Bank</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -71871,16 +71871,16 @@
         <v>1.3</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>1.337992970073233</v>
+        <v>1.896019305497195</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>1.21553748337628</v>
+        <v>1.643619122876333</v>
       </c>
       <c r="G233" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H233" s="4" t="n">
-        <v>10.0295993134081</v>
+        <v>7.665974711918914</v>
       </c>
       <c r="I233" s="2" t="n">
         <v>1</v>
@@ -71974,12 +71974,12 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Dayspring Bank</t>
+          <t>FIDELITY BANK</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -71991,16 +71991,16 @@
         <v>1.23</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>1.058210250494092</v>
+        <v>0.127031632849783</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>1.729802413914201</v>
+        <v>1.847738815382945</v>
       </c>
       <c r="G236" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H236" s="4" t="n">
-        <v>10.7144471836167</v>
+        <v>20.31900232233945</v>
       </c>
       <c r="I236" s="2" t="n">
         <v>1</v>
@@ -72014,12 +72014,12 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>FIDELITY BANK</t>
+          <t>Dayspring Bank</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -72031,16 +72031,16 @@
         <v>1.23</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>0.127031632849783</v>
+        <v>1.058210250494092</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>1.847738815382945</v>
+        <v>1.729802413914201</v>
       </c>
       <c r="G237" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H237" s="4" t="n">
-        <v>20.31900232233945</v>
+        <v>10.7144471836167</v>
       </c>
       <c r="I237" s="2" t="n">
         <v>1</v>
@@ -72054,12 +72054,12 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>First Bankers Trust Company, National Association</t>
+          <t>Citizens State Bank</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -72071,16 +72071,16 @@
         <v>1.22</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>0.6789267821828032</v>
+        <v>1.65308781606644</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>1.279115836437378</v>
+        <v>1.992047593430255</v>
       </c>
       <c r="G238" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H238" s="4" t="n">
-        <v>9.995171215491732</v>
+        <v>12.94870156899756</v>
       </c>
       <c r="I238" s="2" t="n">
         <v>1</v>
@@ -72094,12 +72094,12 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Citizens State Bank</t>
+          <t>MutualOne Bank</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -72111,16 +72111,16 @@
         <v>1.22</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>1.65308781606644</v>
+        <v>0.8829170441622175</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>1.992047593430255</v>
+        <v>5.919405373574457</v>
       </c>
       <c r="G239" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H239" s="4" t="n">
-        <v>12.94870156899756</v>
+        <v>21.08499357326478</v>
       </c>
       <c r="I239" s="2" t="n">
         <v>1</v>
@@ -72134,12 +72134,12 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>MutualOne Bank</t>
+          <t>First Bankers Trust Company, National Association</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -72151,16 +72151,16 @@
         <v>1.22</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>0.8829170441622175</v>
+        <v>0.6789267821828032</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>5.919405373574457</v>
+        <v>1.279115836437378</v>
       </c>
       <c r="G240" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H240" s="4" t="n">
-        <v>21.08499357326478</v>
+        <v>9.995171215491732</v>
       </c>
       <c r="I240" s="2" t="n">
         <v>1</v>
@@ -72374,12 +72374,12 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>PriorityOne Bank</t>
+          <t>Metro Bank</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -72391,16 +72391,16 @@
         <v>1.18</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>2.033157683052361</v>
+        <v>1.412633988558846</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>1.580840539758269</v>
+        <v>1.177971478918872</v>
       </c>
       <c r="G246" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H246" s="4" t="n">
-        <v>11.88978819421625</v>
+        <v>14.68410852062221</v>
       </c>
       <c r="I246" s="2" t="n">
         <v>1</v>
@@ -72414,12 +72414,12 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Metro Bank</t>
+          <t>PriorityOne Bank</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -72431,16 +72431,16 @@
         <v>1.18</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>1.412633988558846</v>
+        <v>2.033157683052361</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>1.177971478918872</v>
+        <v>1.580840539758269</v>
       </c>
       <c r="G247" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H247" s="4" t="n">
-        <v>14.68410852062221</v>
+        <v>11.88978819421625</v>
       </c>
       <c r="I247" s="2" t="n">
         <v>1</v>
@@ -72654,12 +72654,12 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>First National Bank, Ames, Iowa</t>
+          <t>The Evangeline Bank and Trust Company</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -72671,16 +72671,16 @@
         <v>1.11</v>
       </c>
       <c r="E253" s="4" t="n">
-        <v>1.231976324030421</v>
+        <v>1.794739334838052</v>
       </c>
       <c r="F253" s="4" t="n">
-        <v>1.406877496761673</v>
+        <v>1.243808380812272</v>
       </c>
       <c r="G253" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H253" s="4" t="n">
-        <v>9.864433219099881</v>
+        <v>14.22422377920831</v>
       </c>
       <c r="I253" s="2" t="n">
         <v>1</v>
@@ -72694,12 +72694,12 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>St. Louis Bank</t>
+          <t>Liberty Savings Bank, F.S.B.</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -72711,16 +72711,16 @@
         <v>1.11</v>
       </c>
       <c r="E254" s="4" t="n">
-        <v>0.9208712668076099</v>
+        <v>0.3630882422885627</v>
       </c>
       <c r="F254" s="4" t="n">
-        <v>2.866832327379008</v>
+        <v>1.42020190112022</v>
       </c>
       <c r="G254" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H254" s="4" t="n">
-        <v>8.810467580179219</v>
+        <v>9.613861492588665</v>
       </c>
       <c r="I254" s="2" t="n">
         <v>1</v>
@@ -72734,12 +72734,12 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Bank of Labor</t>
+          <t>St. Louis Bank</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -72751,16 +72751,16 @@
         <v>1.11</v>
       </c>
       <c r="E255" s="4" t="n">
-        <v>0.9098887802012977</v>
+        <v>0.9208712668076099</v>
       </c>
       <c r="F255" s="4" t="n">
-        <v>3.148982224457223</v>
+        <v>2.866832327379008</v>
       </c>
       <c r="G255" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H255" s="4" t="n">
-        <v>7.986686557780284</v>
+        <v>8.810467580179219</v>
       </c>
       <c r="I255" s="2" t="n">
         <v>1</v>
@@ -72774,12 +72774,12 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>The Evangeline Bank and Trust Company</t>
+          <t>Bank of Labor</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -72791,16 +72791,16 @@
         <v>1.11</v>
       </c>
       <c r="E256" s="4" t="n">
-        <v>1.794739334838052</v>
+        <v>0.9098887802012977</v>
       </c>
       <c r="F256" s="4" t="n">
-        <v>1.243808380812272</v>
+        <v>3.148982224457223</v>
       </c>
       <c r="G256" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H256" s="4" t="n">
-        <v>14.22422377920831</v>
+        <v>7.986686557780284</v>
       </c>
       <c r="I256" s="2" t="n">
         <v>1</v>
@@ -72854,12 +72854,12 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Liberty Savings Bank, F.S.B.</t>
+          <t>First National Bank, Ames, Iowa</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -72871,16 +72871,16 @@
         <v>1.11</v>
       </c>
       <c r="E258" s="4" t="n">
-        <v>0.3630882422885627</v>
+        <v>1.231976324030421</v>
       </c>
       <c r="F258" s="4" t="n">
-        <v>1.42020190112022</v>
+        <v>1.406877496761673</v>
       </c>
       <c r="G258" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H258" s="4" t="n">
-        <v>9.613861492588665</v>
+        <v>9.864433219099881</v>
       </c>
       <c r="I258" s="2" t="n">
         <v>1</v>
@@ -72934,12 +72934,12 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Generations Bank</t>
+          <t>Pioneer Bank</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -72951,16 +72951,16 @@
         <v>1.09</v>
       </c>
       <c r="E260" s="4" t="n">
-        <v>1.193588459251441</v>
+        <v>2.584451053423047</v>
       </c>
       <c r="F260" s="4" t="n">
-        <v>1.505403275882761</v>
+        <v>1.713686081117447</v>
       </c>
       <c r="G260" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H260" s="4" t="n">
-        <v>11.51487194324723</v>
+        <v>12.31683734673634</v>
       </c>
       <c r="I260" s="2" t="n">
         <v>1</v>
@@ -72974,12 +72974,12 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Pioneer Bank</t>
+          <t>Prime Alliance Bank</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -72991,16 +72991,16 @@
         <v>1.09</v>
       </c>
       <c r="E261" s="4" t="n">
-        <v>2.584451053423047</v>
+        <v>3.406717436871994</v>
       </c>
       <c r="F261" s="4" t="n">
-        <v>1.713686081117447</v>
+        <v>1.598428376090416</v>
       </c>
       <c r="G261" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H261" s="4" t="n">
-        <v>12.31683734673634</v>
+        <v>11.52991071678573</v>
       </c>
       <c r="I261" s="2" t="n">
         <v>1</v>
@@ -73014,12 +73014,12 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Prime Alliance Bank</t>
+          <t>Generations Bank</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -73031,16 +73031,16 @@
         <v>1.09</v>
       </c>
       <c r="E262" s="4" t="n">
-        <v>3.406717436871994</v>
+        <v>1.193588459251441</v>
       </c>
       <c r="F262" s="4" t="n">
-        <v>1.598428376090416</v>
+        <v>1.505403275882761</v>
       </c>
       <c r="G262" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H262" s="4" t="n">
-        <v>11.52991071678573</v>
+        <v>11.51487194324723</v>
       </c>
       <c r="I262" s="2" t="n">
         <v>1</v>
@@ -73094,12 +73094,12 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>The Federal Savings Bank</t>
+          <t>MountainOne Bank</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -73111,16 +73111,16 @@
         <v>1.08</v>
       </c>
       <c r="E264" s="4" t="n">
-        <v>0.05289834276180423</v>
+        <v>1.216161755011887</v>
       </c>
       <c r="F264" s="4" t="n">
-        <v>2.692323182046773</v>
+        <v>1.055384060127373</v>
       </c>
       <c r="G264" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H264" s="4" t="n">
-        <v>15.85592073571901</v>
+        <v>14.74544903112039</v>
       </c>
       <c r="I264" s="2" t="n">
         <v>1</v>
@@ -73134,12 +73134,12 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>MountainOne Bank</t>
+          <t>The First National Bank of Bemidji</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -73151,16 +73151,16 @@
         <v>1.08</v>
       </c>
       <c r="E265" s="4" t="n">
-        <v>1.216161755011887</v>
+        <v>1.422082529240563</v>
       </c>
       <c r="F265" s="4" t="n">
-        <v>1.055384060127373</v>
+        <v>1.990970185572347</v>
       </c>
       <c r="G265" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H265" s="4" t="n">
-        <v>14.74544903112039</v>
+        <v>11.14102017893799</v>
       </c>
       <c r="I265" s="2" t="n">
         <v>1</v>
@@ -73174,12 +73174,12 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>The First National Bank of McGregor</t>
+          <t>The Federal Savings Bank</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -73191,16 +73191,16 @@
         <v>1.08</v>
       </c>
       <c r="E266" s="4" t="n">
-        <v>1.089600776426695</v>
+        <v>0.05289834276180423</v>
       </c>
       <c r="F266" s="4" t="n">
-        <v>2.723311546840959</v>
+        <v>2.692323182046773</v>
       </c>
       <c r="G266" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H266" s="4" t="n">
-        <v>9.54590438824984</v>
+        <v>15.85592073571901</v>
       </c>
       <c r="I266" s="2" t="n">
         <v>1</v>
@@ -73214,12 +73214,12 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>The First National Bank of Bemidji</t>
+          <t>The First National Bank of McGregor</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -73231,16 +73231,16 @@
         <v>1.08</v>
       </c>
       <c r="E267" s="4" t="n">
-        <v>1.422082529240563</v>
+        <v>1.089600776426695</v>
       </c>
       <c r="F267" s="4" t="n">
-        <v>1.990970185572347</v>
+        <v>2.723311546840959</v>
       </c>
       <c r="G267" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H267" s="4" t="n">
-        <v>11.14102017893799</v>
+        <v>9.54590438824984</v>
       </c>
       <c r="I267" s="2" t="n">
         <v>1</v>
@@ -73254,12 +73254,12 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>Brooks Bank, National Association</t>
+          <t>Crescent Bank</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -73271,16 +73271,16 @@
         <v>1.07</v>
       </c>
       <c r="E268" s="4" t="n">
-        <v>2.098607629262268</v>
+        <v>8.336080647785522</v>
       </c>
       <c r="F268" s="4" t="n">
-        <v>2.610187757722602</v>
+        <v>1.279446925552214</v>
       </c>
       <c r="G268" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H268" s="4" t="n">
-        <v>13.31243367136372</v>
+        <v>15.00955363586999</v>
       </c>
       <c r="I268" s="2" t="n">
         <v>1</v>
@@ -73294,12 +73294,12 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>Crescent Bank</t>
+          <t>Brooks Bank, National Association</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -73311,16 +73311,16 @@
         <v>1.07</v>
       </c>
       <c r="E269" s="4" t="n">
-        <v>8.336080647785522</v>
+        <v>2.098607629262268</v>
       </c>
       <c r="F269" s="4" t="n">
-        <v>1.279446925552214</v>
+        <v>2.610187757722602</v>
       </c>
       <c r="G269" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H269" s="4" t="n">
-        <v>15.00955363586999</v>
+        <v>13.31243367136372</v>
       </c>
       <c r="I269" s="2" t="n">
         <v>1</v>
@@ -73334,12 +73334,12 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>Centennial Bank</t>
+          <t>CommerceOne Bank</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -73351,35 +73351,35 @@
         <v>1.06</v>
       </c>
       <c r="E270" s="4" t="n">
-        <v>0.9840674789128397</v>
+        <v>-0.1614620907623072</v>
       </c>
       <c r="F270" s="4" t="n">
-        <v>1.259846509122521</v>
+        <v>0</v>
       </c>
       <c r="G270" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H270" s="4" t="n">
-        <v>9.821456398245259</v>
+        <v>9.014557555189484</v>
       </c>
       <c r="I270" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>Noncurrent loans &gt;2x peers</t>
+          <t>Negative ROA</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>CommerceOne Bank</t>
+          <t>Border Bank</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>ND</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -73391,35 +73391,35 @@
         <v>1.06</v>
       </c>
       <c r="E271" s="4" t="n">
-        <v>-0.1614620907623072</v>
+        <v>1.306148684890688</v>
       </c>
       <c r="F271" s="4" t="n">
-        <v>0</v>
+        <v>1.068984259741989</v>
       </c>
       <c r="G271" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H271" s="4" t="n">
-        <v>9.014557555189484</v>
+        <v>9.070499606461526</v>
       </c>
       <c r="I271" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>Negative ROA</t>
+          <t>Noncurrent loans &gt;2x peers</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>Border Bank</t>
+          <t>Centennial Bank</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -73431,16 +73431,16 @@
         <v>1.06</v>
       </c>
       <c r="E272" s="4" t="n">
-        <v>1.306148684890688</v>
+        <v>0.9840674789128397</v>
       </c>
       <c r="F272" s="4" t="n">
-        <v>1.068984259741989</v>
+        <v>1.259846509122521</v>
       </c>
       <c r="G272" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H272" s="4" t="n">
-        <v>9.070499606461526</v>
+        <v>9.821456398245259</v>
       </c>
       <c r="I272" s="2" t="n">
         <v>1</v>
@@ -73494,12 +73494,12 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>First Southern Bank</t>
+          <t>Security Financial Bank</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>WI</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -73511,16 +73511,16 @@
         <v>1.04</v>
       </c>
       <c r="E274" s="4" t="n">
-        <v>1.370978025043838</v>
+        <v>1.636803755020379</v>
       </c>
       <c r="F274" s="4" t="n">
-        <v>2.997180039744816</v>
+        <v>1.437797259767931</v>
       </c>
       <c r="G274" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H274" s="4" t="n">
-        <v>10.8528880866426</v>
+        <v>9.668487571889223</v>
       </c>
       <c r="I274" s="2" t="n">
         <v>1</v>
@@ -73534,12 +73534,12 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>Security Financial Bank</t>
+          <t>The Freedom Bank of Virginia</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -73551,16 +73551,16 @@
         <v>1.04</v>
       </c>
       <c r="E275" s="4" t="n">
-        <v>1.636803755020379</v>
+        <v>0.4453720121454717</v>
       </c>
       <c r="F275" s="4" t="n">
-        <v>1.437797259767931</v>
+        <v>3.263774737161629</v>
       </c>
       <c r="G275" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H275" s="4" t="n">
-        <v>9.668487571889223</v>
+        <v>11.05912662922399</v>
       </c>
       <c r="I275" s="2" t="n">
         <v>1</v>
@@ -73574,12 +73574,12 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>The Freedom Bank of Virginia</t>
+          <t>First Southern Bank</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -73591,16 +73591,16 @@
         <v>1.04</v>
       </c>
       <c r="E276" s="4" t="n">
-        <v>0.4453720121454717</v>
+        <v>1.370978025043838</v>
       </c>
       <c r="F276" s="4" t="n">
-        <v>3.263774737161629</v>
+        <v>2.997180039744816</v>
       </c>
       <c r="G276" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H276" s="4" t="n">
-        <v>11.05912662922399</v>
+        <v>10.8528880866426</v>
       </c>
       <c r="I276" s="2" t="n">
         <v>1</v>
@@ -73614,12 +73614,12 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>R Bank</t>
+          <t>First Central Savings Bank</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -73631,16 +73631,16 @@
         <v>1.03</v>
       </c>
       <c r="E277" s="4" t="n">
-        <v>0.7242130472999656</v>
+        <v>0.9711513509471805</v>
       </c>
       <c r="F277" s="4" t="n">
-        <v>1.545392246951267</v>
+        <v>1.186253786213162</v>
       </c>
       <c r="G277" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H277" s="4" t="n">
-        <v>9.010771074647959</v>
+        <v>10.29878388484298</v>
       </c>
       <c r="I277" s="2" t="n">
         <v>1</v>
@@ -73654,12 +73654,12 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>First Central Savings Bank</t>
+          <t>R Bank</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -73671,16 +73671,16 @@
         <v>1.03</v>
       </c>
       <c r="E278" s="4" t="n">
-        <v>0.9711513509471805</v>
+        <v>0.7242130472999656</v>
       </c>
       <c r="F278" s="4" t="n">
-        <v>1.186253786213162</v>
+        <v>1.545392246951267</v>
       </c>
       <c r="G278" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H278" s="4" t="n">
-        <v>10.29878388484298</v>
+        <v>9.010771074647959</v>
       </c>
       <c r="I278" s="2" t="n">
         <v>1</v>
@@ -73734,12 +73734,12 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>Presidential Bank, FSB</t>
+          <t>Adirondack Bank</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -73751,35 +73751,35 @@
         <v>1.01</v>
       </c>
       <c r="E280" s="4" t="n">
-        <v>0.4885664705326675</v>
+        <v>-2.117984097366266</v>
       </c>
       <c r="F280" s="4" t="n">
-        <v>1.638145180026194</v>
+        <v>0.7193593555382608</v>
       </c>
       <c r="G280" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H280" s="4" t="n">
-        <v>9.633832027867829</v>
+        <v>7.251912668945216</v>
       </c>
       <c r="I280" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>Noncurrent loans &gt;2x peers</t>
+          <t>Negative ROA</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Adirondack Bank</t>
+          <t>Presidential Bank, FSB</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -73791,23 +73791,23 @@
         <v>1.01</v>
       </c>
       <c r="E281" s="4" t="n">
-        <v>-2.117984097366266</v>
+        <v>0.4885664705326675</v>
       </c>
       <c r="F281" s="4" t="n">
-        <v>0.7193593555382608</v>
+        <v>1.638145180026194</v>
       </c>
       <c r="G281" s="4" t="n">
         <v>0.509</v>
       </c>
       <c r="H281" s="4" t="n">
-        <v>7.251912668945216</v>
+        <v>9.633832027867829</v>
       </c>
       <c r="I281" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>Negative ROA</t>
+          <t>Noncurrent loans &gt;2x peers</t>
         </is>
       </c>
     </row>
